--- a/Entrega final/SUS V 1.0.xlsx
+++ b/Entrega final/SUS V 1.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cris\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cris\Documents\GitHub\trabajo-de-grado-\Entrega final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659964B1-533F-460C-AD39-845F8DEE2423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83614B0-93C9-40F2-B64D-94895CF02842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="79">
   <si>
     <t>No</t>
   </si>
@@ -279,27 +279,6 @@
   </si>
   <si>
     <t>Participante 34</t>
-  </si>
-  <si>
-    <t>Participante 35</t>
-  </si>
-  <si>
-    <t>Participante 36</t>
-  </si>
-  <si>
-    <t>Participante 37</t>
-  </si>
-  <si>
-    <t>Participante 38</t>
-  </si>
-  <si>
-    <t>Participante 39</t>
-  </si>
-  <si>
-    <t>Participante 40</t>
-  </si>
-  <si>
-    <t>Participante 41</t>
   </si>
 </sst>
 </file>
@@ -444,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -503,11 +482,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1063,7 +1046,7 @@
       </c>
       <c r="B2" s="14">
         <f>IF(AVERAGE(M7:M45)&gt;0,AVERAGEIF(M7:M45,"&gt;"&amp;0),0)</f>
-        <v>71.15384615384616</v>
+        <v>75.441176470588232</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="23.25" x14ac:dyDescent="0.35">
@@ -1072,7 +1055,7 @@
       </c>
       <c r="B3" s="15" t="str">
         <f>IF(B2&gt;=78.9,"A",IF(AND(B2&gt;=72.6,B2&lt;=78.8),"B",IF(AND(B2&gt;=62.7,B2&lt;=72.5),"C",IF(AND(B2&gt;=51.7,B2&lt;=62.6),"D",IF(AND(B2 &gt;0,B2&lt;=51.6),"F","")))))</f>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="D3" t="str">
         <f>IF(D2&gt;=78.9,"A",IF(AND(D2&gt;=72.6,D2&lt;=78.8),"B",IF(AND(D2&gt;=62.7,D2&lt;=72.5),"C",IF(AND(D2&gt;=51.7,D2&lt;=62.6),"D",IF(AND(D2 &gt;0,D2&lt;=51.6),"F","")))))</f>
@@ -1158,34 +1141,34 @@
       <c r="A7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="22">
-        <v>5</v>
-      </c>
-      <c r="C7" s="22">
-        <v>3</v>
-      </c>
-      <c r="D7" s="22">
-        <v>3</v>
-      </c>
-      <c r="E7" s="22">
-        <v>4</v>
-      </c>
-      <c r="F7" s="22">
-        <v>5</v>
-      </c>
-      <c r="G7" s="22">
-        <v>3</v>
-      </c>
-      <c r="H7" s="22">
-        <v>4</v>
-      </c>
-      <c r="I7" s="22">
-        <v>1</v>
-      </c>
-      <c r="J7" s="22">
-        <v>5</v>
-      </c>
-      <c r="K7" s="22">
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4">
+        <v>5</v>
+      </c>
+      <c r="G7" s="4">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4">
+        <v>4</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4">
+        <v>5</v>
+      </c>
+      <c r="K7" s="4">
         <v>4</v>
       </c>
       <c r="L7" s="4">
@@ -1205,34 +1188,34 @@
       <c r="A8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="22">
-        <v>4</v>
-      </c>
-      <c r="C8" s="22">
-        <v>1</v>
-      </c>
-      <c r="D8" s="22">
-        <v>5</v>
-      </c>
-      <c r="E8" s="22">
-        <v>2</v>
-      </c>
-      <c r="F8" s="22">
-        <v>4</v>
-      </c>
-      <c r="G8" s="22">
-        <v>1</v>
-      </c>
-      <c r="H8" s="22">
-        <v>3</v>
-      </c>
-      <c r="I8" s="22">
-        <v>1</v>
-      </c>
-      <c r="J8" s="22">
-        <v>4</v>
-      </c>
-      <c r="K8" s="22">
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>4</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>4</v>
+      </c>
+      <c r="K8" s="4">
         <v>2</v>
       </c>
       <c r="L8" s="4">
@@ -1240,7 +1223,7 @@
         <v>27</v>
       </c>
       <c r="M8" s="10">
-        <f t="shared" ref="M8:M45" si="1">IF(L8 &gt; 0,((B8-1)+(5-C8)+(D8-1)+(5-E8)+(F8-1)+(5-G8)+(H8-1)+(5-I8)+(J8-1)+(5-K8))*2.5,0)</f>
+        <f t="shared" ref="M8:M44" si="1">IF(L8 &gt; 0,((B8-1)+(5-C8)+(D8-1)+(5-E8)+(F8-1)+(5-G8)+(H8-1)+(5-I8)+(J8-1)+(5-K8))*2.5,0)</f>
         <v>82.5</v>
       </c>
       <c r="N8" s="11" t="str">
@@ -1252,34 +1235,34 @@
       <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="22">
-        <v>3</v>
-      </c>
-      <c r="C9" s="22">
-        <v>1</v>
-      </c>
-      <c r="D9" s="22">
-        <v>5</v>
-      </c>
-      <c r="E9" s="22">
-        <v>1</v>
-      </c>
-      <c r="F9" s="22">
-        <v>5</v>
-      </c>
-      <c r="G9" s="22">
-        <v>2</v>
-      </c>
-      <c r="H9" s="22">
-        <v>5</v>
-      </c>
-      <c r="I9" s="22">
-        <v>1</v>
-      </c>
-      <c r="J9" s="22">
-        <v>4</v>
-      </c>
-      <c r="K9" s="22">
+      <c r="B9" s="4">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>5</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>4</v>
+      </c>
+      <c r="K9" s="4">
         <v>1</v>
       </c>
       <c r="L9" s="4">
@@ -1299,34 +1282,34 @@
       <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="22">
-        <v>4</v>
-      </c>
-      <c r="C10" s="22">
-        <v>1</v>
-      </c>
-      <c r="D10" s="22">
-        <v>5</v>
-      </c>
-      <c r="E10" s="22">
-        <v>1</v>
-      </c>
-      <c r="F10" s="22">
-        <v>4</v>
-      </c>
-      <c r="G10" s="22">
-        <v>1</v>
-      </c>
-      <c r="H10" s="22">
-        <v>4</v>
-      </c>
-      <c r="I10" s="22">
-        <v>1</v>
-      </c>
-      <c r="J10" s="22">
-        <v>4</v>
-      </c>
-      <c r="K10" s="22">
+      <c r="B10" s="4">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>4</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4">
+        <v>4</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4">
+        <v>4</v>
+      </c>
+      <c r="K10" s="4">
         <v>1</v>
       </c>
       <c r="L10" s="4">
@@ -1346,34 +1329,34 @@
       <c r="A11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="22">
-        <v>5</v>
-      </c>
-      <c r="C11" s="22">
-        <v>1</v>
-      </c>
-      <c r="D11" s="22">
-        <v>5</v>
-      </c>
-      <c r="E11" s="22">
-        <v>4</v>
-      </c>
-      <c r="F11" s="22">
-        <v>5</v>
-      </c>
-      <c r="G11" s="22">
-        <v>1</v>
-      </c>
-      <c r="H11" s="22">
-        <v>5</v>
-      </c>
-      <c r="I11" s="22">
-        <v>1</v>
-      </c>
-      <c r="J11" s="22">
-        <v>5</v>
-      </c>
-      <c r="K11" s="22">
+      <c r="B11" s="4">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4">
+        <v>5</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
+      <c r="J11" s="4">
+        <v>5</v>
+      </c>
+      <c r="K11" s="4">
         <v>4</v>
       </c>
       <c r="L11" s="4">
@@ -1393,34 +1376,34 @@
       <c r="A12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="22">
-        <v>4</v>
-      </c>
-      <c r="C12" s="22">
-        <v>1</v>
-      </c>
-      <c r="D12" s="22">
-        <v>5</v>
-      </c>
-      <c r="E12" s="22">
-        <v>1</v>
-      </c>
-      <c r="F12" s="22">
-        <v>5</v>
-      </c>
-      <c r="G12" s="22">
-        <v>1</v>
-      </c>
-      <c r="H12" s="22">
-        <v>5</v>
-      </c>
-      <c r="I12" s="22">
-        <v>1</v>
-      </c>
-      <c r="J12" s="22">
-        <v>5</v>
-      </c>
-      <c r="K12" s="22">
+      <c r="B12" s="4">
+        <v>4</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>5</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>5</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4">
+        <v>5</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>5</v>
+      </c>
+      <c r="K12" s="4">
         <v>1</v>
       </c>
       <c r="L12" s="4">
@@ -1440,34 +1423,34 @@
       <c r="A13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="22">
-        <v>4</v>
-      </c>
-      <c r="C13" s="22">
-        <v>2</v>
-      </c>
-      <c r="D13" s="22">
-        <v>4</v>
-      </c>
-      <c r="E13" s="22">
-        <v>1</v>
-      </c>
-      <c r="F13" s="22">
-        <v>4</v>
-      </c>
-      <c r="G13" s="22">
-        <v>1</v>
-      </c>
-      <c r="H13" s="22">
-        <v>5</v>
-      </c>
-      <c r="I13" s="22">
-        <v>1</v>
-      </c>
-      <c r="J13" s="22">
-        <v>4</v>
-      </c>
-      <c r="K13" s="22">
+      <c r="B13" s="4">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>4</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>4</v>
+      </c>
+      <c r="K13" s="4">
         <v>1</v>
       </c>
       <c r="L13" s="4">
@@ -1487,34 +1470,34 @@
       <c r="A14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="22">
-        <v>4</v>
-      </c>
-      <c r="C14" s="22">
-        <v>3</v>
-      </c>
-      <c r="D14" s="22">
-        <v>3</v>
-      </c>
-      <c r="E14" s="22">
-        <v>4</v>
-      </c>
-      <c r="F14" s="22">
-        <v>4</v>
-      </c>
-      <c r="G14" s="22">
-        <v>2</v>
-      </c>
-      <c r="H14" s="22">
-        <v>4</v>
-      </c>
-      <c r="I14" s="22">
-        <v>2</v>
-      </c>
-      <c r="J14" s="22">
-        <v>3</v>
-      </c>
-      <c r="K14" s="22">
+      <c r="B14" s="4">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4">
+        <v>3</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4</v>
+      </c>
+      <c r="F14" s="4">
+        <v>4</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4">
+        <v>4</v>
+      </c>
+      <c r="I14" s="4">
+        <v>2</v>
+      </c>
+      <c r="J14" s="4">
+        <v>3</v>
+      </c>
+      <c r="K14" s="4">
         <v>3</v>
       </c>
       <c r="L14" s="4">
@@ -1534,34 +1517,34 @@
       <c r="A15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="22">
-        <v>4</v>
-      </c>
-      <c r="C15" s="22">
-        <v>1</v>
-      </c>
-      <c r="D15" s="22">
-        <v>5</v>
-      </c>
-      <c r="E15" s="22">
-        <v>3</v>
-      </c>
-      <c r="F15" s="22">
-        <v>5</v>
-      </c>
-      <c r="G15" s="22">
-        <v>2</v>
-      </c>
-      <c r="H15" s="22">
-        <v>4</v>
-      </c>
-      <c r="I15" s="22">
-        <v>1</v>
-      </c>
-      <c r="J15" s="22">
-        <v>5</v>
-      </c>
-      <c r="K15" s="22">
+      <c r="B15" s="4">
+        <v>4</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>5</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4">
+        <v>5</v>
+      </c>
+      <c r="G15" s="4">
+        <v>2</v>
+      </c>
+      <c r="H15" s="4">
+        <v>4</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
+        <v>5</v>
+      </c>
+      <c r="K15" s="4">
         <v>2</v>
       </c>
       <c r="L15" s="4">
@@ -1581,34 +1564,34 @@
       <c r="A16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="22">
-        <v>5</v>
-      </c>
-      <c r="C16" s="22">
-        <v>3</v>
-      </c>
-      <c r="D16" s="22">
-        <v>4</v>
-      </c>
-      <c r="E16" s="22">
-        <v>1</v>
-      </c>
-      <c r="F16" s="22">
-        <v>5</v>
-      </c>
-      <c r="G16" s="22">
-        <v>2</v>
-      </c>
-      <c r="H16" s="22">
-        <v>4</v>
-      </c>
-      <c r="I16" s="22">
-        <v>1</v>
-      </c>
-      <c r="J16" s="22">
-        <v>5</v>
-      </c>
-      <c r="K16" s="22">
+      <c r="B16" s="4">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4">
+        <v>3</v>
+      </c>
+      <c r="D16" s="4">
+        <v>4</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>5</v>
+      </c>
+      <c r="G16" s="4">
+        <v>2</v>
+      </c>
+      <c r="H16" s="4">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>5</v>
+      </c>
+      <c r="K16" s="4">
         <v>1</v>
       </c>
       <c r="L16" s="4">
@@ -1628,34 +1611,34 @@
       <c r="A17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="22">
-        <v>5</v>
-      </c>
-      <c r="C17" s="22">
-        <v>3</v>
-      </c>
-      <c r="D17" s="22">
-        <v>3</v>
-      </c>
-      <c r="E17" s="22">
-        <v>2</v>
-      </c>
-      <c r="F17" s="22">
-        <v>5</v>
-      </c>
-      <c r="G17" s="22">
-        <v>1</v>
-      </c>
-      <c r="H17" s="22">
-        <v>5</v>
-      </c>
-      <c r="I17" s="22">
-        <v>1</v>
-      </c>
-      <c r="J17" s="22">
-        <v>5</v>
-      </c>
-      <c r="K17" s="22">
+      <c r="B17" s="4">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3</v>
+      </c>
+      <c r="D17" s="4">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>5</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <v>5</v>
+      </c>
+      <c r="K17" s="4">
         <v>1</v>
       </c>
       <c r="L17" s="4">
@@ -1675,34 +1658,34 @@
       <c r="A18" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="22">
-        <v>5</v>
-      </c>
-      <c r="C18" s="22">
-        <v>1</v>
-      </c>
-      <c r="D18" s="22">
-        <v>1</v>
-      </c>
-      <c r="E18" s="22">
-        <v>1</v>
-      </c>
-      <c r="F18" s="22">
-        <v>5</v>
-      </c>
-      <c r="G18" s="22">
-        <v>2</v>
-      </c>
-      <c r="H18" s="22">
-        <v>5</v>
-      </c>
-      <c r="I18" s="22">
-        <v>1</v>
-      </c>
-      <c r="J18" s="22">
-        <v>5</v>
-      </c>
-      <c r="K18" s="22">
+      <c r="B18" s="4">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>2</v>
+      </c>
+      <c r="H18" s="4">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4">
+        <v>5</v>
+      </c>
+      <c r="K18" s="4">
         <v>3</v>
       </c>
       <c r="L18" s="4">
@@ -1722,34 +1705,34 @@
       <c r="A19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="22">
-        <v>5</v>
-      </c>
-      <c r="C19" s="22">
-        <v>3</v>
-      </c>
-      <c r="D19" s="22">
-        <v>1</v>
-      </c>
-      <c r="E19" s="22">
-        <v>1</v>
-      </c>
-      <c r="F19" s="22">
-        <v>5</v>
-      </c>
-      <c r="G19" s="22">
-        <v>1</v>
-      </c>
-      <c r="H19" s="22">
-        <v>5</v>
-      </c>
-      <c r="I19" s="22">
-        <v>1</v>
-      </c>
-      <c r="J19" s="22">
-        <v>5</v>
-      </c>
-      <c r="K19" s="22">
+      <c r="B19" s="4">
+        <v>5</v>
+      </c>
+      <c r="C19" s="4">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>5</v>
+      </c>
+      <c r="G19" s="4">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>5</v>
+      </c>
+      <c r="K19" s="4">
         <v>1</v>
       </c>
       <c r="L19" s="4">
@@ -1769,325 +1752,325 @@
       <c r="A20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="22">
-        <v>1</v>
-      </c>
-      <c r="C20" s="22">
-        <v>2</v>
-      </c>
-      <c r="D20" s="22">
-        <v>1</v>
-      </c>
-      <c r="E20" s="22">
-        <v>1</v>
-      </c>
-      <c r="F20" s="22">
-        <v>1</v>
-      </c>
-      <c r="G20" s="22">
-        <v>2</v>
-      </c>
-      <c r="H20" s="22">
-        <v>1</v>
-      </c>
-      <c r="I20" s="22">
-        <v>2</v>
-      </c>
-      <c r="J20" s="22">
-        <v>1</v>
-      </c>
-      <c r="K20" s="22">
-        <v>2</v>
+      <c r="B20" s="4">
+        <v>5</v>
+      </c>
+      <c r="C20" s="4">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4">
+        <v>4</v>
+      </c>
+      <c r="E20" s="4">
+        <v>4</v>
+      </c>
+      <c r="F20" s="4">
+        <v>4</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2</v>
+      </c>
+      <c r="H20" s="4">
+        <v>3</v>
+      </c>
+      <c r="I20" s="4">
+        <v>4</v>
+      </c>
+      <c r="J20" s="4">
+        <v>5</v>
+      </c>
+      <c r="K20" s="4">
+        <v>1</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="M20" s="10">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>67.5</v>
       </c>
       <c r="N20" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>C</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="22">
-        <v>5</v>
-      </c>
-      <c r="C21" s="22">
-        <v>3</v>
-      </c>
-      <c r="D21" s="22">
-        <v>4</v>
-      </c>
-      <c r="E21" s="22">
-        <v>4</v>
-      </c>
-      <c r="F21" s="22">
-        <v>4</v>
-      </c>
-      <c r="G21" s="22">
-        <v>2</v>
-      </c>
-      <c r="H21" s="22">
-        <v>3</v>
-      </c>
-      <c r="I21" s="22">
-        <v>4</v>
-      </c>
-      <c r="J21" s="22">
-        <v>5</v>
-      </c>
-      <c r="K21" s="22">
-        <v>1</v>
+      <c r="B21" s="4">
+        <v>3</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>4</v>
+      </c>
+      <c r="G21" s="4">
+        <v>3</v>
+      </c>
+      <c r="H21" s="4">
+        <v>4</v>
+      </c>
+      <c r="I21" s="4">
+        <v>3</v>
+      </c>
+      <c r="J21" s="4">
+        <v>4</v>
+      </c>
+      <c r="K21" s="4">
+        <v>5</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M21" s="10">
         <f t="shared" si="1"/>
-        <v>67.5</v>
+        <v>52.5</v>
       </c>
       <c r="N21" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>D</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="22">
-        <v>1</v>
-      </c>
-      <c r="C22" s="22">
-        <v>2</v>
-      </c>
-      <c r="D22" s="22">
-        <v>1</v>
-      </c>
-      <c r="E22" s="22">
-        <v>2</v>
-      </c>
-      <c r="F22" s="22">
-        <v>1</v>
-      </c>
-      <c r="G22" s="22">
-        <v>1</v>
-      </c>
-      <c r="H22" s="22">
-        <v>1</v>
-      </c>
-      <c r="I22" s="22">
-        <v>1</v>
-      </c>
-      <c r="J22" s="22">
-        <v>1</v>
-      </c>
-      <c r="K22" s="22">
+      <c r="B22" s="4">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>5</v>
+      </c>
+      <c r="G22" s="4">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4">
+        <v>5</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4">
+        <v>5</v>
+      </c>
+      <c r="K22" s="4">
         <v>1</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="M22" s="10">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="N22" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>A</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="22">
-        <v>3</v>
-      </c>
-      <c r="C23" s="22">
-        <v>2</v>
-      </c>
-      <c r="D23" s="22">
-        <v>1</v>
-      </c>
-      <c r="E23" s="22">
-        <v>2</v>
-      </c>
-      <c r="F23" s="22">
-        <v>4</v>
-      </c>
-      <c r="G23" s="22">
-        <v>3</v>
-      </c>
-      <c r="H23" s="22">
-        <v>4</v>
-      </c>
-      <c r="I23" s="22">
-        <v>3</v>
-      </c>
-      <c r="J23" s="22">
-        <v>4</v>
-      </c>
-      <c r="K23" s="22">
-        <v>5</v>
+      <c r="B23" s="4">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>5</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4">
+        <v>5</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4">
+        <v>5</v>
+      </c>
+      <c r="K23" s="4">
+        <v>1</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M23" s="10">
         <f t="shared" si="1"/>
-        <v>52.5</v>
+        <v>92.5</v>
       </c>
       <c r="N23" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>D</v>
+        <v>A</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="22">
-        <v>1</v>
-      </c>
-      <c r="C24" s="22">
-        <v>2</v>
-      </c>
-      <c r="D24" s="22">
-        <v>3</v>
-      </c>
-      <c r="E24" s="22">
-        <v>2</v>
-      </c>
-      <c r="F24" s="22">
-        <v>1</v>
-      </c>
-      <c r="G24" s="22">
-        <v>2</v>
-      </c>
-      <c r="H24" s="22">
-        <v>1</v>
-      </c>
-      <c r="I24" s="22">
-        <v>2</v>
-      </c>
-      <c r="J24" s="22">
-        <v>1</v>
-      </c>
-      <c r="K24" s="22">
-        <v>2</v>
+      <c r="B24" s="4">
+        <v>4</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+      <c r="D24" s="4">
+        <v>4</v>
+      </c>
+      <c r="E24" s="4">
+        <v>4</v>
+      </c>
+      <c r="F24" s="4">
+        <v>3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>3</v>
+      </c>
+      <c r="H24" s="4">
+        <v>4</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2</v>
+      </c>
+      <c r="J24" s="4">
+        <v>4</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="M24" s="10">
         <f t="shared" si="1"/>
-        <v>42.5</v>
+        <v>67.5</v>
       </c>
       <c r="N24" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>C</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="22">
-        <v>5</v>
-      </c>
-      <c r="C25" s="22">
-        <v>1</v>
-      </c>
-      <c r="D25" s="22">
-        <v>1</v>
-      </c>
-      <c r="E25" s="22">
-        <v>1</v>
-      </c>
-      <c r="F25" s="22">
-        <v>5</v>
-      </c>
-      <c r="G25" s="22">
-        <v>1</v>
-      </c>
-      <c r="H25" s="22">
-        <v>5</v>
-      </c>
-      <c r="I25" s="22">
-        <v>1</v>
-      </c>
-      <c r="J25" s="22">
-        <v>5</v>
-      </c>
-      <c r="K25" s="22">
+      <c r="B25" s="4">
+        <v>4</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4">
+        <v>3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>3</v>
+      </c>
+      <c r="H25" s="4">
+        <v>5</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4">
+        <v>3</v>
+      </c>
+      <c r="K25" s="4">
         <v>1</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M25" s="10">
         <f t="shared" si="1"/>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="N25" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>A</v>
+        <v>C</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="22">
-        <v>5</v>
-      </c>
-      <c r="C26" s="22">
-        <v>1</v>
-      </c>
-      <c r="D26" s="22">
-        <v>2</v>
-      </c>
-      <c r="E26" s="22">
-        <v>1</v>
-      </c>
-      <c r="F26" s="22">
-        <v>5</v>
-      </c>
-      <c r="G26" s="22">
-        <v>1</v>
-      </c>
-      <c r="H26" s="22">
-        <v>5</v>
-      </c>
-      <c r="I26" s="22">
-        <v>1</v>
-      </c>
-      <c r="J26" s="22">
-        <v>5</v>
-      </c>
-      <c r="K26" s="22">
+      <c r="B26" s="4">
+        <v>5</v>
+      </c>
+      <c r="C26" s="4">
+        <v>2</v>
+      </c>
+      <c r="D26" s="4">
+        <v>5</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4">
+        <v>5</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4">
+        <v>5</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4">
+        <v>5</v>
+      </c>
+      <c r="K26" s="4">
         <v>1</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M26" s="10">
         <f t="shared" si="1"/>
-        <v>92.5</v>
+        <v>97.5</v>
       </c>
       <c r="N26" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2098,90 +2081,90 @@
       <c r="A27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="22">
-        <v>4</v>
-      </c>
-      <c r="C27" s="22">
-        <v>2</v>
-      </c>
-      <c r="D27" s="22">
-        <v>4</v>
-      </c>
-      <c r="E27" s="22">
-        <v>4</v>
-      </c>
-      <c r="F27" s="22">
-        <v>3</v>
-      </c>
-      <c r="G27" s="22">
-        <v>3</v>
-      </c>
-      <c r="H27" s="22">
-        <v>4</v>
-      </c>
-      <c r="I27" s="22">
-        <v>2</v>
-      </c>
-      <c r="J27" s="22">
-        <v>4</v>
-      </c>
-      <c r="K27" s="22">
+      <c r="B27" s="4">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4">
+        <v>2</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4">
+        <v>2</v>
+      </c>
+      <c r="F27" s="4">
+        <v>5</v>
+      </c>
+      <c r="G27" s="4">
+        <v>2</v>
+      </c>
+      <c r="H27" s="4">
+        <v>4</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4">
+        <v>5</v>
+      </c>
+      <c r="K27" s="4">
         <v>1</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M27" s="10">
         <f t="shared" si="1"/>
-        <v>67.5</v>
+        <v>82.5</v>
       </c>
       <c r="N27" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>A</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="22">
-        <v>4</v>
-      </c>
-      <c r="C28" s="22">
-        <v>2</v>
-      </c>
-      <c r="D28" s="22">
-        <v>4</v>
-      </c>
-      <c r="E28" s="22">
-        <v>4</v>
-      </c>
-      <c r="F28" s="22">
-        <v>3</v>
-      </c>
-      <c r="G28" s="22">
-        <v>3</v>
-      </c>
-      <c r="H28" s="22">
-        <v>5</v>
-      </c>
-      <c r="I28" s="22">
-        <v>1</v>
-      </c>
-      <c r="J28" s="22">
-        <v>3</v>
-      </c>
-      <c r="K28" s="22">
-        <v>1</v>
+      <c r="B28" s="4">
+        <v>5</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4">
+        <v>5</v>
+      </c>
+      <c r="F28" s="4">
+        <v>5</v>
+      </c>
+      <c r="G28" s="4">
+        <v>1</v>
+      </c>
+      <c r="H28" s="4">
+        <v>5</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
+      <c r="J28" s="4">
+        <v>3</v>
+      </c>
+      <c r="K28" s="4">
+        <v>2</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M28" s="10">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="N28" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2192,43 +2175,43 @@
       <c r="A29" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="22">
-        <v>5</v>
-      </c>
-      <c r="C29" s="22">
-        <v>2</v>
-      </c>
-      <c r="D29" s="22">
-        <v>5</v>
-      </c>
-      <c r="E29" s="22">
-        <v>1</v>
-      </c>
-      <c r="F29" s="22">
-        <v>5</v>
-      </c>
-      <c r="G29" s="22">
-        <v>1</v>
-      </c>
-      <c r="H29" s="22">
-        <v>5</v>
-      </c>
-      <c r="I29" s="22">
-        <v>1</v>
-      </c>
-      <c r="J29" s="22">
-        <v>5</v>
-      </c>
-      <c r="K29" s="22">
-        <v>1</v>
+      <c r="B29" s="4">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4">
+        <v>5</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4">
+        <v>5</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4">
+        <v>3</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4">
+        <v>5</v>
+      </c>
+      <c r="K29" s="4">
+        <v>3</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M29" s="10">
         <f t="shared" si="1"/>
-        <v>97.5</v>
+        <v>85</v>
       </c>
       <c r="N29" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2239,128 +2222,128 @@
       <c r="A30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="22">
-        <v>5</v>
-      </c>
-      <c r="C30" s="22">
-        <v>2</v>
-      </c>
-      <c r="D30" s="22">
-        <v>2</v>
-      </c>
-      <c r="E30" s="22">
-        <v>2</v>
-      </c>
-      <c r="F30" s="22">
-        <v>5</v>
-      </c>
-      <c r="G30" s="22">
-        <v>2</v>
-      </c>
-      <c r="H30" s="22">
-        <v>4</v>
-      </c>
-      <c r="I30" s="22">
-        <v>1</v>
-      </c>
-      <c r="J30" s="22">
-        <v>5</v>
-      </c>
-      <c r="K30" s="22">
-        <v>1</v>
+      <c r="B30" s="4">
+        <v>4</v>
+      </c>
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4">
+        <v>5</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2</v>
+      </c>
+      <c r="H30" s="4">
+        <v>5</v>
+      </c>
+      <c r="I30" s="4">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4">
+        <v>5</v>
+      </c>
+      <c r="K30" s="4">
+        <v>3</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M30" s="10">
         <f t="shared" si="1"/>
-        <v>82.5</v>
+        <v>77.5</v>
       </c>
       <c r="N30" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>A</v>
+        <v>B</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="22">
-        <v>5</v>
-      </c>
-      <c r="C31" s="22">
-        <v>3</v>
-      </c>
-      <c r="D31" s="22">
-        <v>3</v>
-      </c>
-      <c r="E31" s="22">
-        <v>5</v>
-      </c>
-      <c r="F31" s="22">
-        <v>5</v>
-      </c>
-      <c r="G31" s="22">
-        <v>1</v>
-      </c>
-      <c r="H31" s="22">
-        <v>5</v>
-      </c>
-      <c r="I31" s="22">
-        <v>1</v>
-      </c>
-      <c r="J31" s="22">
-        <v>3</v>
-      </c>
-      <c r="K31" s="22">
+      <c r="B31" s="4">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4">
+        <v>5</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4">
+        <v>5</v>
+      </c>
+      <c r="H31" s="4">
+        <v>1</v>
+      </c>
+      <c r="I31" s="4">
+        <v>5</v>
+      </c>
+      <c r="J31" s="4">
+        <v>2</v>
+      </c>
+      <c r="K31" s="4">
         <v>2</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M31" s="10">
         <f t="shared" si="1"/>
-        <v>72.5</v>
+        <v>22.5</v>
       </c>
       <c r="N31" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>F</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="22">
-        <v>5</v>
-      </c>
-      <c r="C32" s="22">
-        <v>1</v>
-      </c>
-      <c r="D32" s="22">
-        <v>5</v>
-      </c>
-      <c r="E32" s="22">
-        <v>3</v>
-      </c>
-      <c r="F32" s="22">
-        <v>5</v>
-      </c>
-      <c r="G32" s="22">
-        <v>1</v>
-      </c>
-      <c r="H32" s="22">
-        <v>3</v>
-      </c>
-      <c r="I32" s="22">
-        <v>1</v>
-      </c>
-      <c r="J32" s="22">
-        <v>5</v>
-      </c>
-      <c r="K32" s="22">
+      <c r="B32" s="4">
+        <v>5</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32" s="4">
+        <v>4</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4">
+        <v>5</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <v>4</v>
+      </c>
+      <c r="I32" s="4">
+        <v>2</v>
+      </c>
+      <c r="J32" s="4">
+        <v>4</v>
+      </c>
+      <c r="K32" s="4">
         <v>3</v>
       </c>
       <c r="L32" s="4">
@@ -2369,7 +2352,7 @@
       </c>
       <c r="M32" s="10">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N32" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2380,34 +2363,34 @@
       <c r="A33" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="22">
-        <v>4</v>
-      </c>
-      <c r="C33" s="22">
-        <v>2</v>
-      </c>
-      <c r="D33" s="22">
-        <v>3</v>
-      </c>
-      <c r="E33" s="22">
-        <v>2</v>
-      </c>
-      <c r="F33" s="22">
-        <v>5</v>
-      </c>
-      <c r="G33" s="22">
-        <v>2</v>
-      </c>
-      <c r="H33" s="22">
-        <v>5</v>
-      </c>
-      <c r="I33" s="22">
-        <v>2</v>
-      </c>
-      <c r="J33" s="22">
-        <v>5</v>
-      </c>
-      <c r="K33" s="22">
+      <c r="B33" s="4">
+        <v>5</v>
+      </c>
+      <c r="C33" s="4">
+        <v>2</v>
+      </c>
+      <c r="D33" s="4">
+        <v>2</v>
+      </c>
+      <c r="E33" s="4">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4">
+        <v>5</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2</v>
+      </c>
+      <c r="H33" s="4">
+        <v>5</v>
+      </c>
+      <c r="I33" s="4">
+        <v>2</v>
+      </c>
+      <c r="J33" s="4">
+        <v>5</v>
+      </c>
+      <c r="K33" s="4">
         <v>3</v>
       </c>
       <c r="L33" s="4">
@@ -2427,90 +2410,90 @@
       <c r="A34" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="22">
-        <v>1</v>
-      </c>
-      <c r="C34" s="22">
-        <v>5</v>
-      </c>
-      <c r="D34" s="22">
-        <v>2</v>
-      </c>
-      <c r="E34" s="22">
-        <v>2</v>
-      </c>
-      <c r="F34" s="22">
-        <v>2</v>
-      </c>
-      <c r="G34" s="22">
-        <v>5</v>
-      </c>
-      <c r="H34" s="22">
-        <v>1</v>
-      </c>
-      <c r="I34" s="22">
-        <v>5</v>
-      </c>
-      <c r="J34" s="22">
-        <v>2</v>
-      </c>
-      <c r="K34" s="22">
-        <v>2</v>
+      <c r="B34" s="4">
+        <v>4</v>
+      </c>
+      <c r="C34" s="4">
+        <v>4</v>
+      </c>
+      <c r="D34" s="4">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4">
+        <v>5</v>
+      </c>
+      <c r="F34" s="4">
+        <v>4</v>
+      </c>
+      <c r="G34" s="4">
+        <v>3</v>
+      </c>
+      <c r="H34" s="4">
+        <v>5</v>
+      </c>
+      <c r="I34" s="4">
+        <v>3</v>
+      </c>
+      <c r="J34" s="4">
+        <v>3</v>
+      </c>
+      <c r="K34" s="4">
+        <v>3</v>
       </c>
       <c r="L34" s="4">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="M34" s="10">
         <f t="shared" si="1"/>
-        <v>22.5</v>
+        <v>52.5</v>
       </c>
       <c r="N34" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>D</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="22">
-        <v>5</v>
-      </c>
-      <c r="C35" s="22">
-        <v>2</v>
-      </c>
-      <c r="D35" s="22">
-        <v>4</v>
-      </c>
-      <c r="E35" s="22">
-        <v>2</v>
-      </c>
-      <c r="F35" s="22">
-        <v>5</v>
-      </c>
-      <c r="G35" s="22">
-        <v>1</v>
-      </c>
-      <c r="H35" s="22">
-        <v>4</v>
-      </c>
-      <c r="I35" s="22">
-        <v>2</v>
-      </c>
-      <c r="J35" s="22">
-        <v>4</v>
-      </c>
-      <c r="K35" s="22">
-        <v>3</v>
+      <c r="B35" s="4">
+        <v>5</v>
+      </c>
+      <c r="C35" s="4">
+        <v>2</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4">
+        <v>5</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4">
+        <v>5</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1</v>
+      </c>
+      <c r="J35" s="4">
+        <v>5</v>
+      </c>
+      <c r="K35" s="4">
+        <v>1</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M35" s="10">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N35" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2521,231 +2504,231 @@
       <c r="A36" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="22">
-        <v>5</v>
-      </c>
-      <c r="C36" s="22">
-        <v>2</v>
-      </c>
-      <c r="D36" s="22">
-        <v>2</v>
-      </c>
-      <c r="E36" s="22">
-        <v>2</v>
-      </c>
-      <c r="F36" s="22">
-        <v>5</v>
-      </c>
-      <c r="G36" s="22">
-        <v>2</v>
-      </c>
-      <c r="H36" s="22">
-        <v>5</v>
-      </c>
-      <c r="I36" s="22">
-        <v>2</v>
-      </c>
-      <c r="J36" s="22">
-        <v>5</v>
-      </c>
-      <c r="K36" s="22">
-        <v>3</v>
+      <c r="B36" s="4">
+        <v>4</v>
+      </c>
+      <c r="C36" s="4">
+        <v>3</v>
+      </c>
+      <c r="D36" s="4">
+        <v>3</v>
+      </c>
+      <c r="E36" s="4">
+        <v>4</v>
+      </c>
+      <c r="F36" s="4">
+        <v>3</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2</v>
+      </c>
+      <c r="H36" s="4">
+        <v>5</v>
+      </c>
+      <c r="I36" s="4">
+        <v>2</v>
+      </c>
+      <c r="J36" s="4">
+        <v>4</v>
+      </c>
+      <c r="K36" s="4">
+        <v>4</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M36" s="10">
         <f t="shared" si="1"/>
-        <v>77.5</v>
+        <v>60</v>
       </c>
       <c r="N36" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>B</v>
+        <v>D</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B37" s="22">
-        <v>4</v>
-      </c>
-      <c r="C37" s="22">
-        <v>4</v>
-      </c>
-      <c r="D37" s="22">
-        <v>3</v>
-      </c>
-      <c r="E37" s="22">
-        <v>5</v>
-      </c>
-      <c r="F37" s="22">
-        <v>4</v>
-      </c>
-      <c r="G37" s="22">
-        <v>3</v>
-      </c>
-      <c r="H37" s="22">
-        <v>5</v>
-      </c>
-      <c r="I37" s="22">
-        <v>3</v>
-      </c>
-      <c r="J37" s="22">
-        <v>3</v>
-      </c>
-      <c r="K37" s="22">
+      <c r="B37" s="4">
+        <v>5</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2</v>
+      </c>
+      <c r="D37" s="4">
+        <v>5</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>5</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2</v>
+      </c>
+      <c r="H37" s="4">
+        <v>3</v>
+      </c>
+      <c r="I37" s="4">
+        <v>3</v>
+      </c>
+      <c r="J37" s="4">
+        <v>2</v>
+      </c>
+      <c r="K37" s="4">
         <v>3</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M37" s="10">
         <f t="shared" si="1"/>
-        <v>52.5</v>
+        <v>72.5</v>
       </c>
       <c r="N37" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>D</v>
+        <v>C</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="22">
-        <v>1</v>
-      </c>
-      <c r="C38" s="22">
-        <v>1</v>
-      </c>
-      <c r="D38" s="22">
-        <v>1</v>
-      </c>
-      <c r="E38" s="22">
-        <v>1</v>
-      </c>
-      <c r="F38" s="22">
-        <v>1</v>
-      </c>
-      <c r="G38" s="22">
-        <v>1</v>
-      </c>
-      <c r="H38" s="22">
-        <v>1</v>
-      </c>
-      <c r="I38" s="22">
-        <v>1</v>
-      </c>
-      <c r="J38" s="22">
-        <v>1</v>
-      </c>
-      <c r="K38" s="22">
-        <v>1</v>
+      <c r="B38" s="4">
+        <v>4</v>
+      </c>
+      <c r="C38" s="4">
+        <v>2</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4">
+        <v>2</v>
+      </c>
+      <c r="F38" s="4">
+        <v>4</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2</v>
+      </c>
+      <c r="H38" s="4">
+        <v>4</v>
+      </c>
+      <c r="I38" s="4">
+        <v>2</v>
+      </c>
+      <c r="J38" s="4">
+        <v>3</v>
+      </c>
+      <c r="K38" s="4">
+        <v>3</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M38" s="10">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="N38" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>C</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="22">
-        <v>5</v>
-      </c>
-      <c r="C39" s="22">
-        <v>2</v>
-      </c>
-      <c r="D39" s="22">
-        <v>1</v>
-      </c>
-      <c r="E39" s="22">
-        <v>1</v>
-      </c>
-      <c r="F39" s="22">
-        <v>5</v>
-      </c>
-      <c r="G39" s="22">
-        <v>1</v>
-      </c>
-      <c r="H39" s="22">
-        <v>5</v>
-      </c>
-      <c r="I39" s="22">
-        <v>1</v>
-      </c>
-      <c r="J39" s="22">
-        <v>5</v>
-      </c>
-      <c r="K39" s="22">
-        <v>1</v>
+      <c r="B39" s="4">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4">
+        <v>2</v>
+      </c>
+      <c r="D39" s="4">
+        <v>3</v>
+      </c>
+      <c r="E39" s="4">
+        <v>2</v>
+      </c>
+      <c r="F39" s="4">
+        <v>4</v>
+      </c>
+      <c r="G39" s="4">
+        <v>3</v>
+      </c>
+      <c r="H39" s="4">
+        <v>5</v>
+      </c>
+      <c r="I39" s="4">
+        <v>3</v>
+      </c>
+      <c r="J39" s="4">
+        <v>2</v>
+      </c>
+      <c r="K39" s="4">
+        <v>3</v>
       </c>
       <c r="L39" s="4">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M39" s="10">
         <f t="shared" si="1"/>
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="N39" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>A</v>
+        <v>D</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="22">
-        <v>1</v>
-      </c>
-      <c r="C40" s="22">
-        <v>1</v>
-      </c>
-      <c r="D40" s="22">
-        <v>2</v>
-      </c>
-      <c r="E40" s="22">
-        <v>1</v>
-      </c>
-      <c r="F40" s="22">
-        <v>1</v>
-      </c>
-      <c r="G40" s="22">
-        <v>1</v>
-      </c>
-      <c r="H40" s="22">
-        <v>1</v>
-      </c>
-      <c r="I40" s="22">
-        <v>2</v>
-      </c>
-      <c r="J40" s="22">
-        <v>1</v>
-      </c>
-      <c r="K40" s="22">
-        <v>2</v>
+      <c r="B40" s="4">
+        <v>2</v>
+      </c>
+      <c r="C40" s="4">
+        <v>2</v>
+      </c>
+      <c r="D40" s="4">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4">
+        <v>3</v>
+      </c>
+      <c r="G40" s="4">
+        <v>4</v>
+      </c>
+      <c r="H40" s="4">
+        <v>4</v>
+      </c>
+      <c r="I40" s="4">
+        <v>4</v>
+      </c>
+      <c r="J40" s="4">
+        <v>3</v>
+      </c>
+      <c r="K40" s="4">
+        <v>4</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="M40" s="10">
         <f t="shared" si="1"/>
-        <v>47.5</v>
+        <v>45</v>
       </c>
       <c r="N40" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2753,333 +2736,116 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="22">
-        <v>4</v>
-      </c>
-      <c r="C41" s="22">
-        <v>3</v>
-      </c>
-      <c r="D41" s="22">
-        <v>3</v>
-      </c>
-      <c r="E41" s="22">
-        <v>4</v>
-      </c>
-      <c r="F41" s="22">
-        <v>3</v>
-      </c>
-      <c r="G41" s="22">
-        <v>2</v>
-      </c>
-      <c r="H41" s="22">
-        <v>5</v>
-      </c>
-      <c r="I41" s="22">
-        <v>2</v>
-      </c>
-      <c r="J41" s="22">
-        <v>4</v>
-      </c>
-      <c r="K41" s="22">
-        <v>4</v>
-      </c>
-      <c r="L41" s="4">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="M41" s="10">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N41" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="24"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B42" s="22">
-        <v>5</v>
-      </c>
-      <c r="C42" s="22">
-        <v>2</v>
-      </c>
-      <c r="D42" s="22">
-        <v>5</v>
-      </c>
-      <c r="E42" s="22">
-        <v>1</v>
-      </c>
-      <c r="F42" s="22">
-        <v>5</v>
-      </c>
-      <c r="G42" s="22">
-        <v>2</v>
-      </c>
-      <c r="H42" s="22">
-        <v>3</v>
-      </c>
-      <c r="I42" s="22">
-        <v>3</v>
-      </c>
-      <c r="J42" s="22">
-        <v>2</v>
-      </c>
-      <c r="K42" s="22">
-        <v>3</v>
-      </c>
-      <c r="L42" s="4">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="M42" s="10">
-        <f t="shared" si="1"/>
-        <v>72.5</v>
-      </c>
-      <c r="N42" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>C</v>
-      </c>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="24"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B43" s="22">
-        <v>1</v>
-      </c>
-      <c r="C43" s="22">
-        <v>1</v>
-      </c>
-      <c r="D43" s="22">
-        <v>2</v>
-      </c>
-      <c r="E43" s="22">
-        <v>2</v>
-      </c>
-      <c r="F43" s="22">
-        <v>1</v>
-      </c>
-      <c r="G43" s="22">
-        <v>2</v>
-      </c>
-      <c r="H43" s="22">
-        <v>2</v>
-      </c>
-      <c r="I43" s="22">
-        <v>1</v>
-      </c>
-      <c r="J43" s="22">
-        <v>2</v>
-      </c>
-      <c r="K43" s="22">
-        <v>1</v>
-      </c>
-      <c r="L43" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="M43" s="10">
-        <f t="shared" si="1"/>
-        <v>52.5</v>
-      </c>
-      <c r="N43" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>D</v>
-      </c>
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="24"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="22">
-        <v>4</v>
-      </c>
-      <c r="C44" s="22">
-        <v>2</v>
-      </c>
-      <c r="D44" s="22">
-        <v>2</v>
-      </c>
-      <c r="E44" s="22">
-        <v>2</v>
-      </c>
-      <c r="F44" s="22">
-        <v>4</v>
-      </c>
-      <c r="G44" s="22">
-        <v>2</v>
-      </c>
-      <c r="H44" s="22">
-        <v>4</v>
-      </c>
-      <c r="I44" s="22">
-        <v>2</v>
-      </c>
-      <c r="J44" s="22">
-        <v>3</v>
-      </c>
-      <c r="K44" s="22">
-        <v>3</v>
-      </c>
-      <c r="L44" s="4">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="M44" s="10">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="N44" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>C</v>
-      </c>
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="24"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="22">
-        <v>1</v>
-      </c>
-      <c r="C45" s="22">
-        <v>2</v>
-      </c>
-      <c r="D45" s="22">
-        <v>1</v>
-      </c>
-      <c r="E45" s="22">
-        <v>2</v>
-      </c>
-      <c r="F45" s="22">
-        <v>1</v>
-      </c>
-      <c r="G45" s="22">
-        <v>2</v>
-      </c>
-      <c r="H45" s="22">
-        <v>1</v>
-      </c>
-      <c r="I45" s="22">
-        <v>2</v>
-      </c>
-      <c r="J45" s="22">
-        <v>1</v>
-      </c>
-      <c r="K45" s="22">
-        <v>2</v>
-      </c>
-      <c r="L45" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="M45" s="10">
-        <f>IF(L45 &gt; 0,((B45-1)+(5-C45)+(D45-1)+(5-E45)+(F45-1)+(5-G45)+(H45-1)+(5-I45)+(J45-1)+(5-K45))*2.5,0)</f>
-        <v>37.5</v>
-      </c>
-      <c r="N45" s="11" t="str">
-        <f t="shared" si="2"/>
-        <v>F</v>
-      </c>
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="24"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" s="23">
-        <v>3</v>
-      </c>
-      <c r="C46" s="23">
-        <v>2</v>
-      </c>
-      <c r="D46" s="23">
-        <v>3</v>
-      </c>
-      <c r="E46" s="23">
-        <v>2</v>
-      </c>
-      <c r="F46" s="23">
-        <v>4</v>
-      </c>
-      <c r="G46" s="23">
-        <v>3</v>
-      </c>
-      <c r="H46" s="23">
-        <v>5</v>
-      </c>
-      <c r="I46" s="23">
-        <v>3</v>
-      </c>
-      <c r="J46" s="23">
-        <v>2</v>
-      </c>
-      <c r="K46" s="23">
-        <v>3</v>
-      </c>
-      <c r="L46" s="4">
-        <f t="shared" ref="L46:L47" si="3">SUM(B46:K46)</f>
-        <v>30</v>
-      </c>
-      <c r="M46" s="10">
-        <f t="shared" ref="M46:M47" si="4">IF(L46 &gt; 0,((B46-1)+(5-C46)+(D46-1)+(5-E46)+(F46-1)+(5-G46)+(H46-1)+(5-I46)+(J46-1)+(5-K46))*2.5,0)</f>
-        <v>60</v>
-      </c>
-      <c r="N46" s="11" t="str">
-        <f t="shared" ref="N46:N47" si="5">IF(M46&gt;=78.9,"A",IF(AND(M46&gt;=72.6,M46&lt;=78.8),"B",IF(AND(M46&gt;=62.7,M46&lt;=72.5),"C",IF(AND(M46&gt;=51.7,M46&lt;=62.6),"D",IF(AND(M46 &gt;0,M46&lt;=51.6),"F","")))))</f>
-        <v>D</v>
-      </c>
+      <c r="A46" s="22"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="23"/>
+      <c r="N46" s="24"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B47" s="24">
-        <v>2</v>
-      </c>
-      <c r="C47" s="24">
-        <v>2</v>
-      </c>
-      <c r="D47" s="24">
-        <v>3</v>
-      </c>
-      <c r="E47" s="24">
-        <v>3</v>
-      </c>
-      <c r="F47" s="24">
-        <v>3</v>
-      </c>
-      <c r="G47" s="24">
-        <v>4</v>
-      </c>
-      <c r="H47" s="24">
-        <v>4</v>
-      </c>
-      <c r="I47" s="24">
-        <v>4</v>
-      </c>
-      <c r="J47" s="24">
-        <v>3</v>
-      </c>
-      <c r="K47" s="24">
-        <v>4</v>
-      </c>
-      <c r="L47" s="4">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="M47" s="10">
-        <f t="shared" si="4"/>
-        <v>45</v>
-      </c>
-      <c r="N47" s="11" t="str">
-        <f t="shared" si="5"/>
-        <v>F</v>
-      </c>
+      <c r="A47" s="22"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="23"/>
+      <c r="N47" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Entrega final/SUS V 1.0.xlsx
+++ b/Entrega final/SUS V 1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cris\Documents\GitHub\trabajo-de-grado-\Entrega final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\trabajo-de-grado-\Entrega final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83614B0-93C9-40F2-B64D-94895CF02842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F6A6F-B359-477E-8E57-4E306C92C631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="3" r:id="rId1"/>
@@ -1219,15 +1219,15 @@
         <v>2</v>
       </c>
       <c r="L8" s="4">
-        <f t="shared" ref="L8:L45" si="0">SUM(B8:K8)</f>
+        <f t="shared" ref="L8:L40" si="0">SUM(B8:K8)</f>
         <v>27</v>
       </c>
       <c r="M8" s="10">
-        <f t="shared" ref="M8:M44" si="1">IF(L8 &gt; 0,((B8-1)+(5-C8)+(D8-1)+(5-E8)+(F8-1)+(5-G8)+(H8-1)+(5-I8)+(J8-1)+(5-K8))*2.5,0)</f>
+        <f t="shared" ref="M8:M40" si="1">IF(L8 &gt; 0,((B8-1)+(5-C8)+(D8-1)+(5-E8)+(F8-1)+(5-G8)+(H8-1)+(5-I8)+(J8-1)+(5-K8))*2.5,0)</f>
         <v>82.5</v>
       </c>
       <c r="N8" s="11" t="str">
-        <f t="shared" ref="N8:N45" si="2">IF(M8&gt;=78.9,"A",IF(AND(M8&gt;=72.6,M8&lt;=78.8),"B",IF(AND(M8&gt;=62.7,M8&lt;=72.5),"C",IF(AND(M8&gt;=51.7,M8&lt;=62.6),"D",IF(AND(M8 &gt;0,M8&lt;=51.6),"F","")))))</f>
+        <f t="shared" ref="N8:N40" si="2">IF(M8&gt;=78.9,"A",IF(AND(M8&gt;=72.6,M8&lt;=78.8),"B",IF(AND(M8&gt;=62.7,M8&lt;=72.5),"C",IF(AND(M8&gt;=51.7,M8&lt;=62.6),"D",IF(AND(M8 &gt;0,M8&lt;=51.6),"F","")))))</f>
         <v>A</v>
       </c>
     </row>
@@ -2935,9 +2935,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" style="20" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" style="20" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
